--- a/data/trans_dic/IP31KM04_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 19,32</t>
+          <t>5,82; 18,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 20,63</t>
+          <t>4,12; 15,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 16,94</t>
+          <t>6,47; 15,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 41,13</t>
+          <t>23,25; 39,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,01; 40,75</t>
+          <t>26,02; 42,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,17; 37,13</t>
+          <t>26,49; 38,62</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 33,24</t>
+          <t>21,32; 40,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,33; 41,55</t>
+          <t>14,42; 32,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 34,32</t>
+          <t>20,55; 33,48</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,14; 47,81</t>
+          <t>38,3; 70,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,84; 72,86</t>
+          <t>28,04; 49,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,73; 59,39</t>
+          <t>35,29; 55,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,29; 97,46</t>
+          <t>87,16; 98,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,07; 98,69</t>
+          <t>84,53; 97,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,62; 97,04</t>
+          <t>89,35; 97,24</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 24,21</t>
+          <t>10,86; 27,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,68; 28,23</t>
+          <t>8,09; 24,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,16; 24,1</t>
+          <t>11,54; 23,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,65; 70,85</t>
+          <t>44,13; 60,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,34; 63,47</t>
+          <t>54,91; 70,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,24; 64,75</t>
+          <t>51,77; 62,91</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,44; 67,6</t>
+          <t>59,21; 72,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59,62; 72,69</t>
+          <t>52,37; 67,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58,85; 68,8</t>
+          <t>58,5; 67,81</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37,04; 46,6</t>
+          <t>43,48; 50,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,44; 50,23</t>
+          <t>41,2; 48,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,45; 47,45</t>
+          <t>43,27; 48,28</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>11746</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3478; 13797</t>
+          <t>3504; 11398</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4387; 15394</t>
+          <t>2261; 8694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9423; 24741</t>
+          <t>7454; 17894</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36969</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76702</t>
+          <t>69568</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15948; 51677</t>
+          <t>26728; 45343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30354; 51512</t>
+          <t>25849; 42090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53361; 93590</t>
+          <t>56771; 82749</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33002</t>
+          <t>29916</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8575; 18465</t>
+          <t>12216; 23016</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14432; 26856</t>
+          <t>7802; 17351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25614; 41247</t>
+          <t>22893; 37302</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40879</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>62502</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18915; 33315</t>
+          <t>26737; 49121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30023; 54910</t>
+          <t>19759; 34603</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53271; 86148</t>
+          <t>49509; 78374</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>37554</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>70573</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>28827; 33331</t>
+          <t>34497; 39014</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35453; 40186</t>
+          <t>29897; 34583</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66394; 72702</t>
+          <t>66964; 72881</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>15443</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3581; 10723</t>
+          <t>5127; 13192</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6281; 15183</t>
+          <t>3583; 10877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11924; 23636</t>
+          <t>10563; 21654</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>78538</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>76768</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164212</t>
+          <t>150547</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>68833; 87636</t>
+          <t>62035; 85375</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73403; 98409</t>
+          <t>66898; 85670</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148397; 180494</t>
+          <t>135833; 165072</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>113</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>78457</t>
+          <t>103658</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>102922</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>181378</t>
+          <t>186594</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68758; 86978</t>
+          <t>93040; 113915</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91911; 112059</t>
+          <t>72225; 92522</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>166450; 194591</t>
+          <t>172611; 200051</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>408</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>278064</t>
+          <t>320299</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>241923; 304384</t>
+          <t>298651; 346673</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>316080; 374094</t>
+          <t>254684; 298384</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>579463; 663286</t>
+          <t>564640; 630113</t>
         </is>
       </c>
     </row>
